--- a/stores picture/好口味.xlsx
+++ b/stores picture/好口味.xlsx
@@ -570,7 +570,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -578,7 +578,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -586,7 +586,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -594,7 +594,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
